--- a/tame_output/ON/bt/strategyON_20240923.xlsx
+++ b/tame_output/ON/bt/strategyON_20240923.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>46.4%</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-39.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-47.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.2%</t>
+          <t>-70.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.2%</t>
+          <t>422.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-573.1%</t>
+          <t>-574.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-49.3%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.6%</t>
+          <t>114.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.9%</t>
+          <t>-320.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-69.9%</t>
+          <t>-71.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.8%</t>
+          <t>133.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>122.6%</t>
+          <t>122.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>138.4%</t>
+          <t>137.7%</t>
         </is>
       </c>
     </row>
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.852561626529771</v>
+        <v>-3.935467157686771</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.043292121142208</v>
+        <v>2.010129908679408</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.240520115457577</v>
+        <v>1.157614584300577</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.328985265342411</v>
+        <v>4.279241946648211</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.084162019699273</v>
+        <v>-4.167067550856272</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.970854634048002</v>
+        <v>1.937692421585202</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.240520115457577</v>
+        <v>1.157614584300577</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.349187935516005</v>
+        <v>4.299444616821805</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.134213565228492</v>
+        <v>-4.217119096385492</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.934440251903196</v>
+        <v>1.901278039440396</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.240520115457577</v>
+        <v>1.157614584300577</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.332794171582887</v>
+        <v>4.283050852888687</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.309320397804937</v>
+        <v>-4.392225928961937</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.824649432466085</v>
+        <v>1.791487220003285</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.240520115457577</v>
+        <v>1.157614584300577</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.293046085176353</v>
+        <v>4.243302766482154</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.113220244374414</v>
+        <v>-4.196125775531414</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.910112112835234</v>
+        <v>1.876949900372434</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.4366202688881</v>
+        <v>1.3537147377311</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.417728796231607</v>
+        <v>4.367985477537408</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.96019485226113</v>
+        <v>-4.043100383418129</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.070493269253452</v>
+        <v>2.037331056790652</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.589645661001384</v>
+        <v>1.506740129844384</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.608715031072482</v>
+        <v>4.558971712378282</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.9885021661344</v>
+        <v>-4.0714076972914</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.246636568612437</v>
+        <v>2.213474356149637</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.589645661001384</v>
+        <v>1.506740129844384</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.796181255980775</v>
+        <v>4.746437937286575</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.155095391247922</v>
+        <v>-4.238000922404922</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.14940222992111</v>
+        <v>2.116240017458311</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.423052435887861</v>
+        <v>1.340146904730861</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.665628272266744</v>
+        <v>4.615884953572544</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.132059597886356</v>
+        <v>-4.214965129043356</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.162292949927454</v>
+        <v>2.129130737464655</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.423052435887861</v>
+        <v>1.340146904730861</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.669304674928462</v>
+        <v>4.619561356234262</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.10281361743066</v>
+        <v>-4.185719148587659</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.171609397233228</v>
+        <v>2.138447184770428</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.423052435887861</v>
+        <v>1.340146904730861</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.666922730051957</v>
+        <v>4.617179411357757</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.209739165308511</v>
+        <v>-4.29264469646551</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.126132417239723</v>
+        <v>2.092970204776923</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.31612688801001</v>
+        <v>1.23322135685301</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.600060640482882</v>
+        <v>4.550317321788682</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.35475772381576</v>
+        <v>-4.437663254972759</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.069553795980058</v>
+        <v>2.036391583517258</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.171108329502762</v>
+        <v>1.088202798345762</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.514478307521767</v>
+        <v>4.464734988827566</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.473099489600477</v>
+        <v>-4.556005020757476</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.122148328923924</v>
+        <v>2.088986116461124</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.181794368065652</v>
+        <v>1.098888836908652</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.620821169917254</v>
+        <v>4.571077851223054</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.524509911921185</v>
+        <v>-4.607415443078184</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.099369857121579</v>
+        <v>2.06620764465878</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.181794368065652</v>
+        <v>1.098888836908652</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.618606867043193</v>
+        <v>4.568863548348993</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.603929363128937</v>
+        <v>-4.686834894285936</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.067505204712768</v>
+        <v>2.034342992249968</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.181794368065652</v>
+        <v>1.098888836908652</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.618509995117482</v>
+        <v>4.568766676423282</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.699392361046154</v>
+        <v>-4.782297892203154</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.029313899103924</v>
+        <v>1.996151686641124</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.181794368065652</v>
+        <v>1.098888836908652</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.618503888675525</v>
+        <v>4.568760569981325</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.635016450195439</v>
+        <v>-4.717921981352439</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.053160660006821</v>
+        <v>2.019998447544021</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.246170278916367</v>
+        <v>1.163264747759367</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.655225831748565</v>
+        <v>4.605482513054365</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.690385612327633</v>
+        <v>-4.773291143484633</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.036746812901669</v>
+        <v>2.00358460043887</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.246170278916367</v>
+        <v>1.163264747759367</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.660959649496291</v>
+        <v>4.611216330802091</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.708604079325242</v>
+        <v>-4.791509610482241</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.028997789445559</v>
+        <v>1.995835576982759</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.221063841660525</v>
+        <v>1.138158310503525</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.645434150485719</v>
+        <v>4.595690831791519</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.620397245177664</v>
+        <v>-4.703302776334663</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.084154915954909</v>
+        <v>2.050992703492109</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.221063841660525</v>
+        <v>1.138158310503525</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.665308543336037</v>
+        <v>4.615565224641838</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.514362249972354</v>
+        <v>-4.597267781129354</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.11026961456176</v>
+        <v>2.07710740209896</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.221063841660525</v>
+        <v>1.138158310503525</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.649009243860765</v>
+        <v>4.599265925166565</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.331150586839259</v>
+        <v>-4.414056117996259</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.185985229279044</v>
+        <v>2.152823016816244</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.221063841660525</v>
+        <v>1.138158310503525</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.65144019332481</v>
+        <v>4.60169687463061</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.259429139825408</v>
+        <v>-4.342334670982408</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.180464993932474</v>
+        <v>2.147302781469674</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.292785288674375</v>
+        <v>1.209879757517375</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.660264247381011</v>
+        <v>4.61052092868681</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.237056114217702</v>
+        <v>-4.319961645374701</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.136329950096728</v>
+        <v>2.103167737633928</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.304041039787277</v>
+        <v>1.221135508630277</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.613933443969923</v>
+        <v>4.564190125275723</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456728</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.270072410128447</v>
+        <v>-4.352977941285446</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.308321636617785</v>
+        <v>2.275159424154985</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.234603663120525</v>
+        <v>1.151698131963525</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.757469222855227</v>
+        <v>4.707725904161028</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883675</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.258544774478838</v>
+        <v>-4.341450305635838</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.304853916705878</v>
+        <v>2.271691704243078</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.293604321321888</v>
+        <v>1.210698790164888</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.784790843604294</v>
+        <v>4.735047524910094</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236296</v>
+        <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.355886275821207</v>
+        <v>-4.438791806978206</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.269585428690719</v>
+        <v>2.236423216227919</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.249184139156399</v>
+        <v>1.166278607999399</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.761806846826789</v>
+        <v>4.71206352813259</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427682</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.441742305161173</v>
+        <v>-4.524647836318173</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.236494099147571</v>
+        <v>2.20333188668477</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.206808069930264</v>
+        <v>1.123902538773264</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.737632287483946</v>
+        <v>4.687888968789746</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.450579102577293</v>
+        <v>-4.533484633734292</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.215378582001625</v>
+        <v>2.182216369538825</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.199365897288914</v>
+        <v>1.116460366131914</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.715586185719638</v>
+        <v>4.665842867025438</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.541961665142751</v>
+        <v>-4.624867196299751</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.188990068020491</v>
+        <v>2.155827855557691</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.162801012569569</v>
+        <v>1.079895481412569</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.70381176593308</v>
+        <v>4.654068447238881</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889189</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.530254947155745</v>
+        <v>-4.613160478312745</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.295801013039561</v>
+        <v>2.26263880057676</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.174507730556575</v>
+        <v>1.091602199399575</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.812964054549552</v>
+        <v>4.763220735855352</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409565</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.430591443072083</v>
+        <v>-4.513496974229082</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.33869875340443</v>
+        <v>2.30553654094163</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.237694813760262</v>
+        <v>1.154789282603262</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.853908643203169</v>
+        <v>4.804165324508968</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.440907541238435</v>
+        <v>-4.523813072395434</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.547477147415948</v>
+        <v>2.514314934953148</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.237694813760262</v>
+        <v>1.154789282603262</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.066813476481227</v>
+        <v>5.017070157787026</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762285</v>
+        <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.440813573221062</v>
+        <v>-4.523719104378062</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.546693401534986</v>
+        <v>2.513531189072186</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.23806467510758</v>
+        <v>1.15515914395058</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.066214060201707</v>
+        <v>5.016470741507507</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988016</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.448032397420906</v>
+        <v>-4.530937928577906</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.538037857799402</v>
+        <v>2.504875645336602</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.23806467510758</v>
+        <v>1.15515914395058</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.060446046146061</v>
+        <v>5.010702727451861</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.447083974302868</v>
+        <v>-4.529989505459867</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.538417227046618</v>
+        <v>2.505255014583818</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.23806467510758</v>
+        <v>1.15515914395058</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.060446046146061</v>
+        <v>5.010702727451861</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.604152432558491</v>
+        <v>-4.687057963715491</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.48831745172546</v>
+        <v>2.455155239262661</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.23806467510758</v>
+        <v>1.15515914395058</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.073173654127153</v>
+        <v>5.023430335432953</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.59816018576968</v>
+        <v>-4.681065716926679</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.492660348865373</v>
+        <v>2.459498136402573</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.23806467510758</v>
+        <v>1.15515914395058</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.075119652551541</v>
+        <v>5.025376333857341</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.509602224638912</v>
+        <v>-4.592507755795912</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.521737669335448</v>
+        <v>2.488575456872649</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.23806467510758</v>
+        <v>1.15515914395058</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.06877378856931</v>
+        <v>5.019030469875109</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.491843147135838</v>
+        <v>-4.574748678292837</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.528149977775674</v>
+        <v>2.494987765312874</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.23806467510758</v>
+        <v>1.15515914395058</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.068082466008305</v>
+        <v>5.018339147314105</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.39221299608677</v>
+        <v>-4.47511852724377</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.580784224103888</v>
+        <v>2.547622011641088</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.337694826156647</v>
+        <v>1.254789294999648</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.140642742546333</v>
+        <v>5.090899423852132</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.775357097455269</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.441612504775781</v>
+        <v>-4.524518035932781</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.750178686127009</v>
+        <v>2.71701647366421</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.347953659588392</v>
+        <v>1.265048128431392</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.335952308104106</v>
+        <v>5.286208989409906</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.74907805896313</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.234928031133405</v>
+        <v>-4.317833562290405</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.820041148686822</v>
+        <v>2.786878936224022</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.554638133230768</v>
+        <v>1.471732602073768</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.447151665392393</v>
+        <v>5.397408346698193</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.74028438916254</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.269084926130931</v>
+        <v>-4.351990457287931</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.808379904341916</v>
+        <v>2.775217691879117</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.471054363689956</v>
+        <v>1.388148832532956</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.399002917322011</v>
+        <v>5.34925959862781</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652382</v>
+        <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.176495447069475</v>
+        <v>-4.259400978226474</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.198912809956167</v>
+        <v>3.165750597493367</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.471054363689956</v>
+        <v>1.388148832532956</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.752500031311678</v>
+        <v>5.702756712617479</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108671</v>
+        <v>3.809055905108669</v>
       </c>
       <c r="C2091" t="n">
         <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.236384074893025</v>
+        <v>-4.319289606050025</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.17952047039385</v>
+        <v>3.14635825793105</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.456932449002491</v>
+        <v>1.374026917845491</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.748589994066303</v>
+        <v>5.698846675372103</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103561</v>
+        <v>3.83520244110356</v>
       </c>
       <c r="C2092" t="n">
         <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.184167765096683</v>
+        <v>-4.267073296253683</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.250236935635914</v>
+        <v>3.217074723173114</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.456932449002491</v>
+        <v>1.374026917845491</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.79841993538983</v>
+        <v>5.74867661669563</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047744</v>
+        <v>3.821827147047742</v>
       </c>
       <c r="C2093" t="n">
         <v>4.933074436198346</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.152270248011438</v>
+        <v>-4.235175779168437</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.271809912680023</v>
+        <v>3.238647700217223</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.488829966087737</v>
+        <v>1.405924434930737</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.826372415850988</v>
+        <v>5.776629097156788</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650752</v>
+        <v>3.825268416650751</v>
       </c>
       <c r="C2094" t="n">
         <v>4.928712020237543</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.167025572211578</v>
+        <v>-4.249931103368578</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.261545367039164</v>
+        <v>3.228383154576364</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.488829966087737</v>
+        <v>1.405924434930737</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.822009999890185</v>
+        <v>5.772266681195985</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.754585438803955</v>
+        <v>3.74511645011825</v>
       </c>
       <c r="C2095" t="n">
         <v>4.919636523653823</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.115219307687835</v>
+        <v>-4.125927446340452</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.273192376264941</v>
+        <v>3.268909120803895</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.54063623061148</v>
+        <v>1.529928091958863</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.844018262020711</v>
+        <v>5.837593378829141</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240923.xlsx
+++ b/tame_output/ON/bt/strategyON_20240923.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.3%</t>
+          <t>-70.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.4%</t>
+          <t>422.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-574.2%</t>
+          <t>-581.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-52.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>114.1%</t>
+          <t>114.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-71.0%</t>
+          <t>-78.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.5%</t>
+          <t>131.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>122.2%</t>
+          <t>120.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>137.7%</t>
+          <t>133.3%</t>
         </is>
       </c>
     </row>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800098</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.74557314866085</v>
+        <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.730570473395088</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.74127833279115</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285648</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.74058140139947</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256371</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701</v>
+        <v>3.689942600701001</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790802</v>
+        <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437329</v>
+        <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298397</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
@@ -48971,7 +48971,7 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960218</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
@@ -48994,7 +48994,7 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353535</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
@@ -49017,7 +49017,7 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113278</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
@@ -49040,7 +49040,7 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113686</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.79448684401644</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
@@ -49086,7 +49086,7 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307671</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394111</v>
+        <v>3.723789705394113</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456728</v>
+        <v>3.71560744645673</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
@@ -49178,7 +49178,7 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883676</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
@@ -49201,7 +49201,7 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236295</v>
+        <v>3.717150699236297</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
@@ -49224,7 +49224,7 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.705201079427683</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
@@ -49247,7 +49247,7 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.691835499610382</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
@@ -49270,7 +49270,7 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667454</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
@@ -49293,7 +49293,7 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.67397837488919</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
@@ -49316,7 +49316,7 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409566</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
@@ -49339,7 +49339,7 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452573</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
@@ -49362,7 +49362,7 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762284</v>
+        <v>3.623960959762286</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
@@ -49385,7 +49385,7 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988017</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
@@ -49408,7 +49408,7 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740921</v>
+        <v>3.647907242740923</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
@@ -49431,7 +49431,7 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663627</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
@@ -49454,7 +49454,7 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424771</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
@@ -49477,7 +49477,7 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149219</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
@@ -49500,7 +49500,7 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383092</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
@@ -49523,7 +49523,7 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720999</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
@@ -49546,7 +49546,7 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455269</v>
+        <v>3.775357097455273</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
@@ -49569,7 +49569,7 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.74907805896313</v>
+        <v>3.749078058963134</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
@@ -49592,7 +49592,7 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.74028438916254</v>
+        <v>3.740284389162544</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
@@ -49615,7 +49615,7 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.78248211565238</v>
+        <v>3.782482115652384</v>
       </c>
       <c r="C2090" t="n">
         <v>4.869867413097705</v>
@@ -49638,7 +49638,7 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108669</v>
+        <v>3.809055905108672</v>
       </c>
       <c r="C2091" t="n">
         <v>4.874430524664808</v>
@@ -49661,7 +49661,7 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.83520244110356</v>
+        <v>3.835202441103563</v>
       </c>
       <c r="C2092" t="n">
         <v>4.924260465988335</v>
@@ -49684,7 +49684,7 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047742</v>
+        <v>3.821827147047745</v>
       </c>
       <c r="C2093" t="n">
         <v>4.933074436198346</v>
@@ -49707,7 +49707,7 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650751</v>
+        <v>3.825268416650754</v>
       </c>
       <c r="C2094" t="n">
         <v>4.928712020237543</v>
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.74511645011825</v>
+        <v>3.745116450118253</v>
       </c>
       <c r="C2095" t="n">
         <v>4.919636523653823</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.125927446340452</v>
+        <v>-4.200466479998666</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.268909120803895</v>
+        <v>3.239093507340609</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.529928091958863</v>
+        <v>1.455389058300648</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.837593378829141</v>
+        <v>5.792869958634213</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240923.xlsx
+++ b/tame_output/ON/bt/strategyON_20240923.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>114.4%</t>
+          <t>116.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>98.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>180.3%</t>
+          <t>186.6%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-39.7%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-70.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.2%</t>
+          <t>422.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-581.6%</t>
+          <t>-573.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-52.3%</t>
+          <t>-42.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>114.7%</t>
+          <t>113.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.7%</t>
+          <t>-320.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-70.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.8%</t>
+          <t>136.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>120.4%</t>
+          <t>125.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>133.3%</t>
+          <t>144.5%</t>
         </is>
       </c>
     </row>
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.935467157686771</v>
+        <v>-3.852561626529771</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.010129908679408</v>
+        <v>2.043292121142208</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.157614584300577</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.279241946648211</v>
+        <v>4.328985265342411</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.167067550856272</v>
+        <v>-4.084162019699273</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.937692421585202</v>
+        <v>1.970854634048002</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.157614584300577</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.299444616821805</v>
+        <v>4.349187935516005</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.217119096385492</v>
+        <v>-4.134213565228492</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.901278039440396</v>
+        <v>1.934440251903196</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.157614584300577</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.283050852888687</v>
+        <v>4.332794171582887</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800098</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.392225928961937</v>
+        <v>-4.309320397804937</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.791487220003285</v>
+        <v>1.824649432466085</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.157614584300577</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.243302766482154</v>
+        <v>4.293046085176353</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.74557314866085</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.196125775531414</v>
+        <v>-4.113220244374414</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.876949900372434</v>
+        <v>1.910112112835234</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.3537147377311</v>
+        <v>1.4366202688881</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.367985477537408</v>
+        <v>4.417728796231607</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395088</v>
+        <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.043100383418129</v>
+        <v>-3.96019485226113</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.037331056790652</v>
+        <v>2.070493269253452</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.506740129844384</v>
+        <v>1.589645661001384</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.558971712378282</v>
+        <v>4.608715031072482</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74127833279115</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.0714076972914</v>
+        <v>-3.9885021661344</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.213474356149637</v>
+        <v>2.246636568612437</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.506740129844384</v>
+        <v>1.589645661001384</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.746437937286575</v>
+        <v>4.796181255980775</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.238000922404922</v>
+        <v>-4.155095391247922</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.116240017458311</v>
+        <v>2.14940222992111</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.340146904730861</v>
+        <v>1.423052435887861</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.615884953572544</v>
+        <v>4.665628272266744</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285648</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.214965129043356</v>
+        <v>-4.132059597886356</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.129130737464655</v>
+        <v>2.162292949927454</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.340146904730861</v>
+        <v>1.423052435887861</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.619561356234262</v>
+        <v>4.669304674928462</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.74058140139947</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.185719148587659</v>
+        <v>-4.10281361743066</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.138447184770428</v>
+        <v>2.171609397233228</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.340146904730861</v>
+        <v>1.423052435887861</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.617179411357757</v>
+        <v>4.666922730051957</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256371</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.29264469646551</v>
+        <v>-4.209739165308511</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.092970204776923</v>
+        <v>2.126132417239723</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.23322135685301</v>
+        <v>1.31612688801001</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.550317321788682</v>
+        <v>4.600060640482882</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701001</v>
+        <v>3.689942600701</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.437663254972759</v>
+        <v>-4.35475772381576</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.036391583517258</v>
+        <v>2.069553795980058</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.088202798345762</v>
+        <v>1.171108329502762</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.464734988827566</v>
+        <v>4.514478307521767</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.556005020757476</v>
+        <v>-4.473099489600477</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.088986116461124</v>
+        <v>2.122148328923924</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.098888836908652</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.571077851223054</v>
+        <v>4.620821169917254</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790803</v>
+        <v>3.714879051790802</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.607415443078184</v>
+        <v>-4.524509911921185</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.06620764465878</v>
+        <v>2.099369857121579</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.098888836908652</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.568863548348993</v>
+        <v>4.618606867043193</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437329</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.686834894285936</v>
+        <v>-4.603929363128937</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.034342992249968</v>
+        <v>2.067505204712768</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.098888836908652</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.568766676423282</v>
+        <v>4.618509995117482</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298397</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.782297892203154</v>
+        <v>-4.699392361046154</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.996151686641124</v>
+        <v>2.029313899103924</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.098888836908652</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.568760569981325</v>
+        <v>4.618503888675525</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218</v>
+        <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.717921981352439</v>
+        <v>-4.635016450195439</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.019998447544021</v>
+        <v>2.053160660006821</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.163264747759367</v>
+        <v>1.246170278916367</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.605482513054365</v>
+        <v>4.655225831748565</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353535</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.773291143484633</v>
+        <v>-4.690385612327633</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.00358460043887</v>
+        <v>2.036746812901669</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.163264747759367</v>
+        <v>1.246170278916367</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.611216330802091</v>
+        <v>4.660959649496291</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113278</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.791509610482241</v>
+        <v>-4.708604079325242</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.995835576982759</v>
+        <v>2.028997789445559</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.138158310503525</v>
+        <v>1.221063841660525</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.595690831791519</v>
+        <v>4.645434150485719</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113686</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.703302776334663</v>
+        <v>-4.620397245177664</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.050992703492109</v>
+        <v>2.084154915954909</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.138158310503525</v>
+        <v>1.221063841660525</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.615565224641838</v>
+        <v>4.665308543336037</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.79448684401644</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.597267781129354</v>
+        <v>-4.514362249972354</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.07710740209896</v>
+        <v>2.11026961456176</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.138158310503525</v>
+        <v>1.221063841660525</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.599265925166565</v>
+        <v>4.649009243860765</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307671</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.414056117996259</v>
+        <v>-4.331150586839259</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.152823016816244</v>
+        <v>2.185985229279044</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.138158310503525</v>
+        <v>1.221063841660525</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.60169687463061</v>
+        <v>4.65144019332481</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.342334670982408</v>
+        <v>-4.259429139825408</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.147302781469674</v>
+        <v>2.180464993932474</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.209879757517375</v>
+        <v>1.292785288674375</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.61052092868681</v>
+        <v>4.660264247381011</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394113</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.319961645374701</v>
+        <v>-4.237056114217702</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.103167737633928</v>
+        <v>2.136329950096728</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.221135508630277</v>
+        <v>1.304041039787277</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.564190125275723</v>
+        <v>4.613933443969923</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.71560744645673</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.352977941285446</v>
+        <v>-4.270072410128447</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.275159424154985</v>
+        <v>2.308321636617785</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.151698131963525</v>
+        <v>1.234603663120525</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.707725904161028</v>
+        <v>4.757469222855227</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883676</v>
+        <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.341450305635838</v>
+        <v>-4.258544774478838</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.271691704243078</v>
+        <v>2.304853916705878</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.210698790164888</v>
+        <v>1.293604321321888</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.735047524910094</v>
+        <v>4.784790843604294</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236297</v>
+        <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.438791806978206</v>
+        <v>-4.355886275821207</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.236423216227919</v>
+        <v>2.269585428690719</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.166278607999399</v>
+        <v>1.249184139156399</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.71206352813259</v>
+        <v>4.761806846826789</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427683</v>
+        <v>3.705201079427682</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.524647836318173</v>
+        <v>-4.441742305161173</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.20333188668477</v>
+        <v>2.236494099147571</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.123902538773264</v>
+        <v>1.206808069930264</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.687888968789746</v>
+        <v>4.737632287483946</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610382</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.99596664734629</v>
+        <v>4.058210005873146</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.533484633734292</v>
+        <v>-4.450579102577293</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.182216369538825</v>
+        <v>2.277621940528481</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.116460366131914</v>
+        <v>1.199365897288914</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.665842867025438</v>
+        <v>4.777829544246495</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667454</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.006131158391339</v>
+        <v>4.068374516918196</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.624867196299751</v>
+        <v>-4.541961665142751</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.155827855557691</v>
+        <v>2.251233426547347</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.079895481412569</v>
+        <v>1.162801012569569</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.654068447238881</v>
+        <v>4.766055124459937</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.67397837488919</v>
+        <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.108259416215606</v>
+        <v>4.170502774742463</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.613160478312745</v>
+        <v>-4.530254947155745</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.26263880057676</v>
+        <v>2.358044371566417</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.091602199399575</v>
+        <v>1.174507730556575</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.763220735855352</v>
+        <v>4.875207413076408</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409566</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.111291754947011</v>
+        <v>4.173535113473868</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.513496974229082</v>
+        <v>-4.430591443072083</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.30553654094163</v>
+        <v>2.400942111931287</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.154789282603262</v>
+        <v>1.237694813760262</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.804165324508968</v>
+        <v>4.916152001730025</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452573</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.324196588225069</v>
+        <v>4.386439946751926</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.523813072395434</v>
+        <v>-4.440907541238435</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.514314934953148</v>
+        <v>2.609720505942804</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.154789282603262</v>
+        <v>1.237694813760262</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.017070157787026</v>
+        <v>5.129056835008083</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762286</v>
+        <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.323375255137159</v>
+        <v>4.385618613664016</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.523719104378062</v>
+        <v>-4.440813573221062</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.513531189072186</v>
+        <v>2.608936760061843</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.15515914395058</v>
+        <v>1.23806467510758</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.016470741507507</v>
+        <v>5.128457418728564</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988017</v>
+        <v>3.633213467988016</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.317607241081513</v>
+        <v>4.379850599608369</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.530937928577906</v>
+        <v>-4.448032397420906</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.504875645336602</v>
+        <v>2.600281216326259</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.15515914395058</v>
+        <v>1.23806467510758</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.010702727451861</v>
+        <v>5.122689404672918</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740923</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.317607241081513</v>
+        <v>4.379850599608369</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.529989505459867</v>
+        <v>-4.447083974302868</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.505255014583818</v>
+        <v>2.600660585573475</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.15515914395058</v>
+        <v>1.23806467510758</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.010702727451861</v>
+        <v>5.122689404672918</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663627</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.330334849062605</v>
+        <v>4.392578207589461</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.687057963715491</v>
+        <v>-4.604152432558491</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.455155239262661</v>
+        <v>2.550560810252317</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.15515914395058</v>
+        <v>1.23806467510758</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.023430335432953</v>
+        <v>5.13541701265401</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424771</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.332280847486992</v>
+        <v>4.394524206013849</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.681065716926679</v>
+        <v>-4.59816018576968</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.459498136402573</v>
+        <v>2.55490370739223</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.15515914395058</v>
+        <v>1.23806467510758</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.025376333857341</v>
+        <v>5.137363011078397</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149219</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.325934983504761</v>
+        <v>4.388178342031618</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.592507755795912</v>
+        <v>-4.509602224638912</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.488575456872649</v>
+        <v>2.583981027862305</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.15515914395058</v>
+        <v>1.23806467510758</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.019030469875109</v>
+        <v>5.131017147096166</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383092</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.325243660943757</v>
+        <v>4.387487019470614</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.574748678292837</v>
+        <v>-4.491843147135838</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.494987765312874</v>
+        <v>2.59039333630253</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.15515914395058</v>
+        <v>1.23806467510758</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.018339147314105</v>
+        <v>5.130325824535162</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720999</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.338025846852344</v>
+        <v>4.400269205379201</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.47511852724377</v>
+        <v>-4.39221299608677</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.547622011641088</v>
+        <v>2.643027582630745</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.254789294999648</v>
+        <v>1.337694826156647</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.090899423852132</v>
+        <v>5.202886101073189</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455273</v>
+        <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.52718011235107</v>
+        <v>4.589423470877927</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.524518035932781</v>
+        <v>-4.441612504775781</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.71701647366421</v>
+        <v>2.812422044653866</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.265048128431392</v>
+        <v>1.347953659588392</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.286208989409906</v>
+        <v>5.398195666630962</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963134</v>
+        <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.514368785453932</v>
+        <v>4.576612143980789</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.317833562290405</v>
+        <v>-4.234928031133405</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.786878936224022</v>
+        <v>2.882284507213679</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.471732602073768</v>
+        <v>1.554638133230768</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.397408346698193</v>
+        <v>5.50939502391925</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162544</v>
+        <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.516370299108037</v>
+        <v>4.578613657634894</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.351990457287931</v>
+        <v>-4.269084926130931</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.775217691879117</v>
+        <v>2.870623262868773</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.388148832532956</v>
+        <v>1.471054363689956</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.34925959862781</v>
+        <v>5.461246275848867</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652384</v>
+        <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.869867413097705</v>
+        <v>4.932110771624561</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.259400978226474</v>
+        <v>-4.176495447069475</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.165750597493367</v>
+        <v>3.261156168483024</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.388148832532956</v>
+        <v>1.471054363689956</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.702756712617479</v>
+        <v>5.814743389838535</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108672</v>
+        <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.874430524664808</v>
+        <v>4.936673883191665</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.319289606050025</v>
+        <v>-4.236384074893025</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.14635825793105</v>
+        <v>3.241763828920706</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.374026917845491</v>
+        <v>1.456932449002491</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.698846675372103</v>
+        <v>5.81083335259316</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103563</v>
+        <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.924260465988335</v>
+        <v>4.986503824515192</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.267073296253683</v>
+        <v>-4.184167765096683</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.217074723173114</v>
+        <v>3.31248029416277</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.374026917845491</v>
+        <v>1.456932449002491</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.74867661669563</v>
+        <v>5.860663293916687</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047745</v>
+        <v>3.821827147047744</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.933074436198346</v>
+        <v>4.995317794725203</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.235175779168437</v>
+        <v>-4.152270248011438</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.238647700217223</v>
+        <v>3.33405327120688</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.405924434930737</v>
+        <v>1.488829966087737</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.776629097156788</v>
+        <v>5.888615774377845</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650754</v>
+        <v>3.825268416650752</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.928712020237543</v>
+        <v>4.9909553787644</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.249931103368578</v>
+        <v>-4.167025572211578</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.228383154576364</v>
+        <v>3.323788725566021</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.405924434930737</v>
+        <v>1.488829966087737</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.772266681195985</v>
+        <v>5.884253358417042</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.745116450118253</v>
+        <v>3.747224332094609</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.919636523653823</v>
+        <v>4.98187988218068</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.200466479998666</v>
+        <v>-4.117560948841667</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.239093507340609</v>
+        <v>3.334499078330265</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.455389058300648</v>
+        <v>1.538294589457648</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.792869958634213</v>
+        <v>5.904856635855269</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240923.xlsx
+++ b/tame_output/ON/bt/strategyON_20240923.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>116.7%</t>
+          <t>114.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>98.7%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>186.6%</t>
+          <t>180.9%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-39.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-47.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.3%</t>
+          <t>-70.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.4%</t>
+          <t>420.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-573.3%</t>
+          <t>-581.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-42.8%</t>
+          <t>-44.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,16 +1242,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.7%</t>
+          <t>114.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.8%</t>
+          <t>-320.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-70.2%</t>
+          <t>-78.5%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>136.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,36 +1418,36 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>85.4%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>56.8%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>94.9%</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>59.4%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>56.9%</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>92.3%</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2023-12-28</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>125.0%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>144.5%</t>
+          <t>45.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2095"/>
+  <dimension ref="A1:G2096"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.852561626529771</v>
+        <v>-3.935467157686771</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.043292121142208</v>
+        <v>2.010129908679408</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.240520115457577</v>
+        <v>1.157614584300577</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.328985265342411</v>
+        <v>4.279241946648211</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.084162019699273</v>
+        <v>-4.167067550856272</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.970854634048002</v>
+        <v>1.937692421585202</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.240520115457577</v>
+        <v>1.157614584300577</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.349187935516005</v>
+        <v>4.299444616821805</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.134213565228492</v>
+        <v>-4.217119096385492</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.934440251903196</v>
+        <v>1.901278039440396</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.240520115457577</v>
+        <v>1.157614584300577</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.332794171582887</v>
+        <v>4.283050852888687</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800098</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.309320397804937</v>
+        <v>-4.392225928961937</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.824649432466085</v>
+        <v>1.791487220003285</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.240520115457577</v>
+        <v>1.157614584300577</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.293046085176353</v>
+        <v>4.243302766482154</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.74557314866085</v>
+        <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.113220244374414</v>
+        <v>-4.196125775531414</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.910112112835234</v>
+        <v>1.876949900372434</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.4366202688881</v>
+        <v>1.3537147377311</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.417728796231607</v>
+        <v>4.367985477537408</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.730570473395088</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.96019485226113</v>
+        <v>-4.043100383418129</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.070493269253452</v>
+        <v>2.037331056790652</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.589645661001384</v>
+        <v>1.506740129844384</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.608715031072482</v>
+        <v>4.558971712378282</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.74127833279115</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.9885021661344</v>
+        <v>-4.0714076972914</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.246636568612437</v>
+        <v>2.213474356149637</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.589645661001384</v>
+        <v>1.506740129844384</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.796181255980775</v>
+        <v>4.746437937286575</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.155095391247922</v>
+        <v>-4.238000922404922</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.14940222992111</v>
+        <v>2.116240017458311</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.423052435887861</v>
+        <v>1.340146904730861</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.665628272266744</v>
+        <v>4.615884953572544</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285648</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.132059597886356</v>
+        <v>-4.214965129043356</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.162292949927454</v>
+        <v>2.129130737464655</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.423052435887861</v>
+        <v>1.340146904730861</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.669304674928462</v>
+        <v>4.619561356234262</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.74058140139947</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.10281361743066</v>
+        <v>-4.185719148587659</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.171609397233228</v>
+        <v>2.138447184770428</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.423052435887861</v>
+        <v>1.340146904730861</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.666922730051957</v>
+        <v>4.617179411357757</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256371</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.209739165308511</v>
+        <v>-4.29264469646551</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.126132417239723</v>
+        <v>2.092970204776923</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.31612688801001</v>
+        <v>1.23322135685301</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.600060640482882</v>
+        <v>4.550317321788682</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701</v>
+        <v>3.689942600701001</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.35475772381576</v>
+        <v>-4.437663254972759</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.069553795980058</v>
+        <v>2.036391583517258</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.171108329502762</v>
+        <v>1.088202798345762</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.514478307521767</v>
+        <v>4.464734988827566</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.473099489600477</v>
+        <v>-4.556005020757476</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.122148328923924</v>
+        <v>2.088986116461124</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.181794368065652</v>
+        <v>1.098888836908652</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.620821169917254</v>
+        <v>4.571077851223054</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790802</v>
+        <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.524509911921185</v>
+        <v>-4.607415443078184</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.099369857121579</v>
+        <v>2.06620764465878</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.181794368065652</v>
+        <v>1.098888836908652</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.618606867043193</v>
+        <v>4.568863548348993</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437329</v>
+        <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.603929363128937</v>
+        <v>-4.686834894285936</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.067505204712768</v>
+        <v>2.034342992249968</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.181794368065652</v>
+        <v>1.098888836908652</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.618509995117482</v>
+        <v>4.568766676423282</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298397</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.699392361046154</v>
+        <v>-4.782297892203154</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.029313899103924</v>
+        <v>1.996151686641124</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.181794368065652</v>
+        <v>1.098888836908652</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.618503888675525</v>
+        <v>4.568760569981325</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960218</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.635016450195439</v>
+        <v>-4.717921981352439</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.053160660006821</v>
+        <v>2.019998447544021</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.246170278916367</v>
+        <v>1.163264747759367</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.655225831748565</v>
+        <v>4.605482513054365</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353535</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.690385612327633</v>
+        <v>-4.773291143484633</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.036746812901669</v>
+        <v>2.00358460043887</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.246170278916367</v>
+        <v>1.163264747759367</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.660959649496291</v>
+        <v>4.611216330802091</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113278</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.708604079325242</v>
+        <v>-4.791509610482241</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.028997789445559</v>
+        <v>1.995835576982759</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.221063841660525</v>
+        <v>1.138158310503525</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.645434150485719</v>
+        <v>4.595690831791519</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113686</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.620397245177664</v>
+        <v>-4.703302776334663</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.084154915954909</v>
+        <v>2.050992703492109</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.221063841660525</v>
+        <v>1.138158310503525</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.665308543336037</v>
+        <v>4.615565224641838</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.79448684401644</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.514362249972354</v>
+        <v>-4.597267781129354</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.11026961456176</v>
+        <v>2.07710740209896</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.221063841660525</v>
+        <v>1.138158310503525</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.649009243860765</v>
+        <v>4.599265925166565</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307671</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.331150586839259</v>
+        <v>-4.414056117996259</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.185985229279044</v>
+        <v>2.152823016816244</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.221063841660525</v>
+        <v>1.138158310503525</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.65144019332481</v>
+        <v>4.60169687463061</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.259429139825408</v>
+        <v>-4.342334670982408</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.180464993932474</v>
+        <v>2.147302781469674</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.292785288674375</v>
+        <v>1.209879757517375</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.660264247381011</v>
+        <v>4.61052092868681</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.723789705394113</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.237056114217702</v>
+        <v>-4.319961645374701</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.136329950096728</v>
+        <v>2.103167737633928</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.304041039787277</v>
+        <v>1.221135508630277</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.613933443969923</v>
+        <v>4.564190125275723</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.71560744645673</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.270072410128447</v>
+        <v>-4.352977941285446</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.308321636617785</v>
+        <v>2.275159424154985</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.234603663120525</v>
+        <v>1.151698131963525</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.757469222855227</v>
+        <v>4.707725904161028</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883675</v>
+        <v>3.713762536883676</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.258544774478838</v>
+        <v>-4.341450305635838</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.304853916705878</v>
+        <v>2.271691704243078</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.293604321321888</v>
+        <v>1.210698790164888</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.784790843604294</v>
+        <v>4.735047524910094</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236296</v>
+        <v>3.717150699236297</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.355886275821207</v>
+        <v>-4.438791806978206</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.269585428690719</v>
+        <v>2.236423216227919</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.249184139156399</v>
+        <v>1.166278607999399</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.761806846826789</v>
+        <v>4.71206352813259</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427682</v>
+        <v>3.705201079427683</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.441742305161173</v>
+        <v>-4.524647836318173</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.236494099147571</v>
+        <v>2.20333188668477</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.206808069930264</v>
+        <v>1.123902538773264</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.737632287483946</v>
+        <v>4.687888968789746</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610382</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.058210005873146</v>
+        <v>4.071387332445631</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.450579102577293</v>
+        <v>-4.533484633734292</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.277621940528481</v>
+        <v>2.257637054638166</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.199365897288914</v>
+        <v>1.116460366131914</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.777829544246495</v>
+        <v>4.741263552124779</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667454</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.068374516918196</v>
+        <v>4.08155184349068</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.541961665142751</v>
+        <v>-4.624867196299751</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.251233426547347</v>
+        <v>2.231248540657032</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.162801012569569</v>
+        <v>1.079895481412569</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.766055124459937</v>
+        <v>4.729489132338221</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.170502774742463</v>
+        <v>4.183680101314948</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.530254947155745</v>
+        <v>-4.613160478312745</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.358044371566417</v>
+        <v>2.338059485676102</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.174507730556575</v>
+        <v>1.091602199399575</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.875207413076408</v>
+        <v>4.838641420954694</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409565</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.173535113473868</v>
+        <v>4.186712440046353</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.430591443072083</v>
+        <v>-4.513496974229082</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.400942111931287</v>
+        <v>2.380957226040972</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.237694813760262</v>
+        <v>1.154789282603262</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.916152001730025</v>
+        <v>4.87958600960831</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.672895177452572</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.386439946751926</v>
+        <v>4.399617273324411</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.440907541238435</v>
+        <v>-4.523813072395434</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.609720505942804</v>
+        <v>2.589735620052489</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.237694813760262</v>
+        <v>1.154789282603262</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.129056835008083</v>
+        <v>5.092490842886368</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.385618613664016</v>
+        <v>4.398795940236501</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.440813573221062</v>
+        <v>-4.523719104378062</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.608936760061843</v>
+        <v>2.588951874171528</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.23806467510758</v>
+        <v>1.15515914395058</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.128457418728564</v>
+        <v>5.091891426606849</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.633213467988016</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.379850599608369</v>
+        <v>4.393027926180855</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.448032397420906</v>
+        <v>-4.530937928577906</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.600281216326259</v>
+        <v>2.580296330435944</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.23806467510758</v>
+        <v>1.15515914395058</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.122689404672918</v>
+        <v>5.086123412551203</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.379850599608369</v>
+        <v>4.393027926180855</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.447083974302868</v>
+        <v>-4.529989505459867</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.600660585573475</v>
+        <v>2.58067569968316</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.23806467510758</v>
+        <v>1.15515914395058</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.122689404672918</v>
+        <v>5.086123412551203</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.392578207589461</v>
+        <v>4.405755534161947</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.604152432558491</v>
+        <v>-4.687057963715491</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.550560810252317</v>
+        <v>2.530575924362003</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.23806467510758</v>
+        <v>1.15515914395058</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.13541701265401</v>
+        <v>5.098851020532295</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.394524206013849</v>
+        <v>4.407701532586334</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.59816018576968</v>
+        <v>-4.681065716926679</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.55490370739223</v>
+        <v>2.534918821501915</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.23806467510758</v>
+        <v>1.15515914395058</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.137363011078397</v>
+        <v>5.100797018956682</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.388178342031618</v>
+        <v>4.401355668604103</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.509602224638912</v>
+        <v>-4.592507755795912</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.583981027862305</v>
+        <v>2.563996141971991</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.23806467510758</v>
+        <v>1.15515914395058</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.131017147096166</v>
+        <v>5.094451154974451</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.387487019470614</v>
+        <v>4.400664346043099</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.491843147135838</v>
+        <v>-4.574748678292837</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.59039333630253</v>
+        <v>2.570408450412216</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.23806467510758</v>
+        <v>1.15515914395058</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.130325824535162</v>
+        <v>5.093759832413447</v>
       </c>
     </row>
     <row r="2086">
@@ -49526,19 +49526,19 @@
         <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.400269205379201</v>
+        <v>4.413446531951686</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.39221299608677</v>
+        <v>-4.47511852724377</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.643027582630745</v>
+        <v>2.62304269674043</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.337694826156647</v>
+        <v>1.254789294999648</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.202886101073189</v>
+        <v>5.166320108951474</v>
       </c>
     </row>
     <row r="2087">
@@ -49549,19 +49549,19 @@
         <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.589423470877927</v>
+        <v>4.602600797450412</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.441612504775781</v>
+        <v>-4.524518035932781</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.812422044653866</v>
+        <v>2.792437158763552</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.347953659588392</v>
+        <v>1.265048128431392</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.398195666630962</v>
+        <v>5.361629674509248</v>
       </c>
     </row>
     <row r="2088">
@@ -49572,19 +49572,19 @@
         <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.576612143980789</v>
+        <v>4.589789470553274</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.234928031133405</v>
+        <v>-4.317833562290405</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.882284507213679</v>
+        <v>2.862299621323364</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.554638133230768</v>
+        <v>1.471732602073768</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.50939502391925</v>
+        <v>5.472829031797535</v>
       </c>
     </row>
     <row r="2089">
@@ -49595,19 +49595,19 @@
         <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.578613657634894</v>
+        <v>4.591790984207379</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.269084926130931</v>
+        <v>-4.351990457287931</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.870623262868773</v>
+        <v>2.850638376978459</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.471054363689956</v>
+        <v>1.388148832532956</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.461246275848867</v>
+        <v>5.424680283727152</v>
       </c>
     </row>
     <row r="2090">
@@ -49618,19 +49618,19 @@
         <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.932110771624561</v>
+        <v>4.945288098197047</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.176495447069475</v>
+        <v>-4.259400978226474</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.261156168483024</v>
+        <v>3.241171282592709</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.471054363689956</v>
+        <v>1.388148832532956</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.814743389838535</v>
+        <v>5.778177397716821</v>
       </c>
     </row>
     <row r="2091">
@@ -49641,19 +49641,19 @@
         <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.936673883191665</v>
+        <v>4.94985120976415</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.236384074893025</v>
+        <v>-4.319289606050025</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.241763828920706</v>
+        <v>3.221778943030392</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.456932449002491</v>
+        <v>1.374026917845491</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.81083335259316</v>
+        <v>5.774267360471445</v>
       </c>
     </row>
     <row r="2092">
@@ -49664,19 +49664,19 @@
         <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.986503824515192</v>
+        <v>4.999681151087677</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.184167765096683</v>
+        <v>-4.267073296253683</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.31248029416277</v>
+        <v>3.292495408272456</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.456932449002491</v>
+        <v>1.374026917845491</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.860663293916687</v>
+        <v>5.824097301794972</v>
       </c>
     </row>
     <row r="2093">
@@ -49687,19 +49687,19 @@
         <v>3.821827147047744</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.995317794725203</v>
+        <v>5.008495121297688</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.152270248011438</v>
+        <v>-4.235175779168437</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.33405327120688</v>
+        <v>3.314068385316565</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.488829966087737</v>
+        <v>1.405924434930737</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.888615774377845</v>
+        <v>5.85204978225613</v>
       </c>
     </row>
     <row r="2094">
@@ -49710,19 +49710,19 @@
         <v>3.825268416650752</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.9909553787644</v>
+        <v>5.004132705336885</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.167025572211578</v>
+        <v>-4.249931103368578</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.323788725566021</v>
+        <v>3.303803839675706</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.488829966087737</v>
+        <v>1.405924434930737</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.884253358417042</v>
+        <v>5.847687366295327</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,45 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.747224332094609</v>
+        <v>3.845044666135745</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.98187988218068</v>
+        <v>4.995057208753165</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.117560948841667</v>
+        <v>-4.200466479998666</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.334499078330265</v>
+        <v>3.314514192439951</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.538294589457648</v>
+        <v>1.455389058300648</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.904856635855269</v>
+        <v>5.868290643733554</v>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" s="2" t="n">
+        <v>45558</v>
+      </c>
+      <c r="B2096" t="n">
+        <v>3.749121335806628</v>
+      </c>
+      <c r="C2096" t="n">
+        <v>4.925741585814661</v>
+      </c>
+      <c r="D2096" t="n">
+        <v>-4.200466479998666</v>
+      </c>
+      <c r="E2096" t="n">
+        <v>3.314514192439951</v>
+      </c>
+      <c r="F2096" t="n">
+        <v>1.455389058300648</v>
+      </c>
+      <c r="G2096" t="n">
+        <v>4.918805382801029</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240923.xlsx
+++ b/tame_output/ON/bt/strategyON_20240923.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>114.4%</t>
+          <t>111.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>180.9%</t>
+          <t>172.4%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-39.7%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-70.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.9%</t>
+          <t>420.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-581.6%</t>
+          <t>-581.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-44.8%</t>
+          <t>-52.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>114.3%</t>
+          <t>113.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.1%</t>
+          <t>-320.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-72.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>87.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>37.4%</t>
         </is>
       </c>
     </row>
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.935467157686771</v>
+        <v>-3.852561626529771</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.010129908679408</v>
+        <v>2.043292121142208</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.157614584300577</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.279241946648211</v>
+        <v>4.328985265342411</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.167067550856272</v>
+        <v>-4.084162019699273</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.937692421585202</v>
+        <v>1.970854634048002</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.157614584300577</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.299444616821805</v>
+        <v>4.349187935516005</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.217119096385492</v>
+        <v>-4.134213565228492</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.901278039440396</v>
+        <v>1.934440251903196</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.157614584300577</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.283050852888687</v>
+        <v>4.332794171582887</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.392225928961937</v>
+        <v>-4.309320397804937</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.791487220003285</v>
+        <v>1.824649432466085</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.157614584300577</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.243302766482154</v>
+        <v>4.293046085176353</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.196125775531414</v>
+        <v>-4.113220244374414</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.876949900372434</v>
+        <v>1.910112112835234</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.3537147377311</v>
+        <v>1.4366202688881</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.367985477537408</v>
+        <v>4.417728796231607</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.043100383418129</v>
+        <v>-3.96019485226113</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.037331056790652</v>
+        <v>2.070493269253452</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.506740129844384</v>
+        <v>1.589645661001384</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.558971712378282</v>
+        <v>4.608715031072482</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.0714076972914</v>
+        <v>-3.9885021661344</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.213474356149637</v>
+        <v>2.246636568612437</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.506740129844384</v>
+        <v>1.589645661001384</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.746437937286575</v>
+        <v>4.796181255980775</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.238000922404922</v>
+        <v>-4.155095391247922</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.116240017458311</v>
+        <v>2.14940222992111</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.340146904730861</v>
+        <v>1.423052435887861</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.615884953572544</v>
+        <v>4.665628272266744</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.214965129043356</v>
+        <v>-4.132059597886356</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.129130737464655</v>
+        <v>2.162292949927454</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.340146904730861</v>
+        <v>1.423052435887861</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.619561356234262</v>
+        <v>4.669304674928462</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.185719148587659</v>
+        <v>-4.10281361743066</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.138447184770428</v>
+        <v>2.171609397233228</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.340146904730861</v>
+        <v>1.423052435887861</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.617179411357757</v>
+        <v>4.666922730051957</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.29264469646551</v>
+        <v>-4.209739165308511</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.092970204776923</v>
+        <v>2.126132417239723</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.23322135685301</v>
+        <v>1.31612688801001</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.550317321788682</v>
+        <v>4.600060640482882</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.437663254972759</v>
+        <v>-4.35475772381576</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.036391583517258</v>
+        <v>2.069553795980058</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.088202798345762</v>
+        <v>1.171108329502762</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.464734988827566</v>
+        <v>4.514478307521767</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.556005020757476</v>
+        <v>-4.473099489600477</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.088986116461124</v>
+        <v>2.122148328923924</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.098888836908652</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.571077851223054</v>
+        <v>4.620821169917254</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.607415443078184</v>
+        <v>-4.524509911921185</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.06620764465878</v>
+        <v>2.099369857121579</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.098888836908652</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.568863548348993</v>
+        <v>4.618606867043193</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.686834894285936</v>
+        <v>-4.603929363128937</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.034342992249968</v>
+        <v>2.067505204712768</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.098888836908652</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.568766676423282</v>
+        <v>4.618509995117482</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.782297892203154</v>
+        <v>-4.699392361046154</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.996151686641124</v>
+        <v>2.029313899103924</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.098888836908652</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.568760569981325</v>
+        <v>4.618503888675525</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.717921981352439</v>
+        <v>-4.635016450195439</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.019998447544021</v>
+        <v>2.053160660006821</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.163264747759367</v>
+        <v>1.246170278916367</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.605482513054365</v>
+        <v>4.655225831748565</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.773291143484633</v>
+        <v>-4.690385612327633</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.00358460043887</v>
+        <v>2.036746812901669</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.163264747759367</v>
+        <v>1.246170278916367</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.611216330802091</v>
+        <v>4.660959649496291</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.791509610482241</v>
+        <v>-4.708604079325242</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.995835576982759</v>
+        <v>2.028997789445559</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.138158310503525</v>
+        <v>1.221063841660525</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.595690831791519</v>
+        <v>4.645434150485719</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.703302776334663</v>
+        <v>-4.620397245177664</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.050992703492109</v>
+        <v>2.084154915954909</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.138158310503525</v>
+        <v>1.221063841660525</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.615565224641838</v>
+        <v>4.665308543336037</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.597267781129354</v>
+        <v>-4.514362249972354</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.07710740209896</v>
+        <v>2.11026961456176</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.138158310503525</v>
+        <v>1.221063841660525</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.599265925166565</v>
+        <v>4.649009243860765</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.414056117996259</v>
+        <v>-4.331150586839259</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.152823016816244</v>
+        <v>2.185985229279044</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.138158310503525</v>
+        <v>1.221063841660525</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.60169687463061</v>
+        <v>4.65144019332481</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.342334670982408</v>
+        <v>-4.259429139825408</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.147302781469674</v>
+        <v>2.180464993932474</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.209879757517375</v>
+        <v>1.292785288674375</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.61052092868681</v>
+        <v>4.660264247381011</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.319961645374701</v>
+        <v>-4.237056114217702</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.103167737633928</v>
+        <v>2.136329950096728</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.221135508630277</v>
+        <v>1.304041039787277</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.564190125275723</v>
+        <v>4.613933443969923</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.352977941285446</v>
+        <v>-4.270072410128447</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.275159424154985</v>
+        <v>2.308321636617785</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.151698131963525</v>
+        <v>1.234603663120525</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.707725904161028</v>
+        <v>4.757469222855227</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.341450305635838</v>
+        <v>-4.258544774478838</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.271691704243078</v>
+        <v>2.304853916705878</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.210698790164888</v>
+        <v>1.293604321321888</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.735047524910094</v>
+        <v>4.784790843604294</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.438791806978206</v>
+        <v>-4.355886275821207</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.236423216227919</v>
+        <v>2.269585428690719</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.166278607999399</v>
+        <v>1.249184139156399</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.71206352813259</v>
+        <v>4.761806846826789</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.524647836318173</v>
+        <v>-4.441742305161173</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.20333188668477</v>
+        <v>2.236494099147571</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.123902538773264</v>
+        <v>1.206808069930264</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.687888968789746</v>
+        <v>4.737632287483946</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691835499610382</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.071387332445631</v>
+        <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.533484633734292</v>
+        <v>-4.531084272504583</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.257637054638166</v>
+        <v>2.183176514030708</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.116460366131914</v>
+        <v>1.171899505946087</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.741263552124779</v>
+        <v>4.699106350913942</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.715544411667454</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.08155184349068</v>
+        <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.624867196299751</v>
+        <v>-4.622466835070042</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.231248540657032</v>
+        <v>2.156788000049574</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.079895481412569</v>
+        <v>1.135334621226742</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.729489132338221</v>
+        <v>4.687331931127384</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.183680101314948</v>
+        <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.613160478312745</v>
+        <v>-4.610760117083036</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.338059485676102</v>
+        <v>2.263598945068644</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.091602199399575</v>
+        <v>1.147041339213749</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.838641420954694</v>
+        <v>4.796484219743856</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409565</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.186712440046353</v>
+        <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.513496974229082</v>
+        <v>-4.511096612999373</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.380957226040972</v>
+        <v>2.306496685433514</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.154789282603262</v>
+        <v>1.210228422417435</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.87958600960831</v>
+        <v>4.837428808397473</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452572</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.399617273324411</v>
+        <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.523813072395434</v>
+        <v>-4.521412711165725</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.589735620052489</v>
+        <v>2.515275079445031</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.154789282603262</v>
+        <v>1.210228422417435</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.092490842886368</v>
+        <v>5.050333641675531</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.398795940236501</v>
+        <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.523719104378062</v>
+        <v>-4.521318743148353</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.588951874171528</v>
+        <v>2.51449133356407</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.15515914395058</v>
+        <v>1.210598283764753</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.091891426606849</v>
+        <v>5.049734225396011</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.633213467988016</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.393027926180855</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.530937928577906</v>
+        <v>-4.528537567348197</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.580296330435944</v>
+        <v>2.505835789828486</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.15515914395058</v>
+        <v>1.210598283764753</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.086123412551203</v>
+        <v>5.043966211340365</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.393027926180855</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.529989505459867</v>
+        <v>-4.527589144230158</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.58067569968316</v>
+        <v>2.506215159075701</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.15515914395058</v>
+        <v>1.210598283764753</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.086123412551203</v>
+        <v>5.043966211340365</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.405755534161947</v>
+        <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.687057963715491</v>
+        <v>-4.684657602485782</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.530575924362003</v>
+        <v>2.456115383754544</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.15515914395058</v>
+        <v>1.210598283764753</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.098851020532295</v>
+        <v>5.056693819321457</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.407701532586334</v>
+        <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.681065716926679</v>
+        <v>-4.67866535569697</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.534918821501915</v>
+        <v>2.460458280894456</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.15515914395058</v>
+        <v>1.210598283764753</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.100797018956682</v>
+        <v>5.058639817745845</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.401355668604103</v>
+        <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.592507755795912</v>
+        <v>-4.590107394566203</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.563996141971991</v>
+        <v>2.489535601364532</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.15515914395058</v>
+        <v>1.210598283764753</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.094451154974451</v>
+        <v>5.052293953763614</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.400664346043099</v>
+        <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.574748678292837</v>
+        <v>-4.572348317063128</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.570408450412216</v>
+        <v>2.495947909804758</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.15515914395058</v>
+        <v>1.210598283764753</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.093759832413447</v>
+        <v>5.051602631202609</v>
       </c>
     </row>
     <row r="2086">
@@ -49526,19 +49526,19 @@
         <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.413446531951686</v>
+        <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.47511852724377</v>
+        <v>-4.472718166014061</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.62304269674043</v>
+        <v>2.548582156132972</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.254789294999648</v>
+        <v>1.310228434813821</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.166320108951474</v>
+        <v>5.124162907740637</v>
       </c>
     </row>
     <row r="2087">
@@ -49549,19 +49549,19 @@
         <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.602600797450412</v>
+        <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.524518035932781</v>
+        <v>-4.522117674703072</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.792437158763552</v>
+        <v>2.717976618156094</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.265048128431392</v>
+        <v>1.320487268245566</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.361629674509248</v>
+        <v>5.31947247329841</v>
       </c>
     </row>
     <row r="2088">
@@ -49572,19 +49572,19 @@
         <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.589789470553274</v>
+        <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.317833562290405</v>
+        <v>-4.315433201060696</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.862299621323364</v>
+        <v>2.787839080715906</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.471732602073768</v>
+        <v>1.527171741887941</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.472829031797535</v>
+        <v>5.430671830586697</v>
       </c>
     </row>
     <row r="2089">
@@ -49595,19 +49595,19 @@
         <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.591790984207379</v>
+        <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.351990457287931</v>
+        <v>-4.349590096058222</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.850638376978459</v>
+        <v>2.776177836371001</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.388148832532956</v>
+        <v>1.443587972347129</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.424680283727152</v>
+        <v>5.382523082516315</v>
       </c>
     </row>
     <row r="2090">
@@ -49618,19 +49618,19 @@
         <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.945288098197047</v>
+        <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.259400978226474</v>
+        <v>-4.257000616996765</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.241171282592709</v>
+        <v>3.16671074198525</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.388148832532956</v>
+        <v>1.443587972347129</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.778177397716821</v>
+        <v>5.736020196505982</v>
       </c>
     </row>
     <row r="2091">
@@ -49641,19 +49641,19 @@
         <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.94985120976415</v>
+        <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.319289606050025</v>
+        <v>-4.316889244820316</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.221778943030392</v>
+        <v>3.147318402422933</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.374026917845491</v>
+        <v>1.429466057659664</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.774267360471445</v>
+        <v>5.732110159260607</v>
       </c>
     </row>
     <row r="2092">
@@ -49664,19 +49664,19 @@
         <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.999681151087677</v>
+        <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.267073296253683</v>
+        <v>-4.264672935023974</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.292495408272456</v>
+        <v>3.218034867664998</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.374026917845491</v>
+        <v>1.429466057659664</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.824097301794972</v>
+        <v>5.781940100584134</v>
       </c>
     </row>
     <row r="2093">
@@ -49687,19 +49687,19 @@
         <v>3.821827147047744</v>
       </c>
       <c r="C2093" t="n">
-        <v>5.008495121297688</v>
+        <v>4.933074436198346</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.235175779168437</v>
+        <v>-4.232775417938728</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.314068385316565</v>
+        <v>3.239607844709107</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.405924434930737</v>
+        <v>1.46136357474491</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.85204978225613</v>
+        <v>5.809892581045292</v>
       </c>
     </row>
     <row r="2094">
@@ -49710,19 +49710,19 @@
         <v>3.825268416650752</v>
       </c>
       <c r="C2094" t="n">
-        <v>5.004132705336885</v>
+        <v>4.928712020237543</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.249931103368578</v>
+        <v>-4.247530742138869</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.303803839675706</v>
+        <v>3.229343299068248</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.405924434930737</v>
+        <v>1.46136357474491</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.847687366295327</v>
+        <v>5.805530165084489</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135745</v>
+        <v>3.845044666135746</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.995057208753165</v>
+        <v>4.919636523653823</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.200466479998666</v>
+        <v>-4.198066118768957</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.314514192439951</v>
+        <v>3.240053651832492</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.455389058300648</v>
+        <v>1.510828198114822</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.868290643733554</v>
+        <v>5.826133442522717</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.749121335806628</v>
+        <v>3.738349511211421</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.925741585814661</v>
+        <v>4.840707459776846</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.200466479998666</v>
+        <v>-4.198066118768957</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.314514192439951</v>
+        <v>3.240053651832492</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.455389058300648</v>
+        <v>1.510828198114822</v>
       </c>
       <c r="G2096" t="n">
-        <v>4.918805382801029</v>
+        <v>4.833771256763214</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240923.xlsx
+++ b/tame_output/ON/bt/strategyON_20240923.xlsx
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013424</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800098</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.74557314866085</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395088</v>
+        <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74127833279115</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285648</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.74058140139947</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256371</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701001</v>
+        <v>3.689942600701</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790803</v>
+        <v>3.714879051790802</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437329</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298397</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
@@ -48971,7 +48971,7 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218</v>
+        <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
@@ -48994,7 +48994,7 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353535</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
@@ -49017,7 +49017,7 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113278</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
@@ -49040,7 +49040,7 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113686</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.79448684401644</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
@@ -49086,7 +49086,7 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307671</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394113</v>
+        <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.71560744645673</v>
+        <v>3.715607446456728</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
@@ -49178,7 +49178,7 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883676</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
@@ -49201,7 +49201,7 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236297</v>
+        <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
@@ -49224,7 +49224,7 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427683</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
@@ -49247,7 +49247,7 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610382</v>
+        <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
@@ -49270,7 +49270,7 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667454</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
@@ -49293,7 +49293,7 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889189</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
@@ -49316,7 +49316,7 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409565</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
@@ -49339,7 +49339,7 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452572</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
@@ -49362,7 +49362,7 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762285</v>
+        <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
@@ -49385,7 +49385,7 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988016</v>
+        <v>3.633213467988014</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
@@ -49408,7 +49408,7 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
@@ -49431,7 +49431,7 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
@@ -49454,7 +49454,7 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
@@ -49477,7 +49477,7 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
@@ -49500,7 +49500,7 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
@@ -49523,7 +49523,7 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
@@ -49546,7 +49546,7 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.775357097455269</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
@@ -49569,7 +49569,7 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.74907805896313</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
@@ -49592,7 +49592,7 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.74028438916254</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
@@ -49615,7 +49615,7 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652382</v>
+        <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
         <v>4.869867413097705</v>
@@ -49638,7 +49638,7 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108671</v>
+        <v>3.809055905108669</v>
       </c>
       <c r="C2091" t="n">
         <v>4.874430524664808</v>
@@ -49661,7 +49661,7 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103561</v>
+        <v>3.83520244110356</v>
       </c>
       <c r="C2092" t="n">
         <v>4.924260465988335</v>
@@ -49684,7 +49684,7 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047744</v>
+        <v>3.821827147047742</v>
       </c>
       <c r="C2093" t="n">
         <v>4.933074436198346</v>
@@ -49707,7 +49707,7 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650752</v>
+        <v>3.825268416650751</v>
       </c>
       <c r="C2094" t="n">
         <v>4.928712020237543</v>
@@ -49730,7 +49730,7 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135746</v>
+        <v>3.845044666135744</v>
       </c>
       <c r="C2095" t="n">
         <v>4.919636523653823</v>
@@ -49753,7 +49753,7 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.738349511211421</v>
+        <v>3.738349511211419</v>
       </c>
       <c r="C2096" t="n">
         <v>4.840707459776846</v>

--- a/tame_output/ON/bt/strategyON_20240923.xlsx
+++ b/tame_output/ON/bt/strategyON_20240923.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>44.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>111.3%</t>
+          <t>114.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>172.4%</t>
+          <t>180.0%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-40.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.7%</t>
+          <t>420.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-581.4%</t>
+          <t>-582.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-52.2%</t>
+          <t>-52.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.5%</t>
+          <t>112.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-72.9%</t>
+          <t>-64.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>134.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,31 +1423,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2023-12-28</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>141.3%</t>
         </is>
       </c>
     </row>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
@@ -49063,16 +49063,16 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.514362249972354</v>
+        <v>-4.6049860698055</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.11026961456176</v>
+        <v>2.074020086628502</v>
       </c>
       <c r="F2066" t="n">
         <v>1.221063841660525</v>
@@ -49092,10 +49092,10 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.331150586839259</v>
+        <v>-4.421774406672405</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.185985229279044</v>
+        <v>2.149735701345786</v>
       </c>
       <c r="F2067" t="n">
         <v>1.221063841660525</v>
@@ -49109,16 +49109,16 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.259429139825408</v>
+        <v>-4.350052959658554</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.180464993932474</v>
+        <v>2.144215465999216</v>
       </c>
       <c r="F2068" t="n">
         <v>1.292785288674375</v>
@@ -49132,16 +49132,16 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394111</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.237056114217702</v>
+        <v>-4.327679934050848</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.136329950096728</v>
+        <v>2.10008042216347</v>
       </c>
       <c r="F2069" t="n">
         <v>1.304041039787277</v>
@@ -49155,16 +49155,16 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456728</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.270072410128447</v>
+        <v>-4.360696229961593</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.308321636617785</v>
+        <v>2.272072108684527</v>
       </c>
       <c r="F2070" t="n">
         <v>1.234603663120525</v>
@@ -49178,16 +49178,16 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.258544774478838</v>
+        <v>-4.349168594311984</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.304853916705878</v>
+        <v>2.268604388772619</v>
       </c>
       <c r="F2071" t="n">
         <v>1.293604321321888</v>
@@ -49201,16 +49201,16 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236295</v>
+        <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.355886275821207</v>
+        <v>-4.446510095654353</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.269585428690719</v>
+        <v>2.23333590075746</v>
       </c>
       <c r="F2072" t="n">
         <v>1.249184139156399</v>
@@ -49224,16 +49224,16 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.705201079427682</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.441742305161173</v>
+        <v>-4.532366124994319</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.236494099147571</v>
+        <v>2.200244571214312</v>
       </c>
       <c r="F2073" t="n">
         <v>1.206808069930264</v>
@@ -49247,16 +49247,16 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.531084272504583</v>
+        <v>-4.621708092337729</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.183176514030708</v>
+        <v>2.14692698609745</v>
       </c>
       <c r="F2074" t="n">
         <v>1.171899505946087</v>
@@ -49276,10 +49276,10 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.622466835070042</v>
+        <v>-4.713090654903188</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.156788000049574</v>
+        <v>2.120538472116316</v>
       </c>
       <c r="F2075" t="n">
         <v>1.135334621226742</v>
@@ -49293,16 +49293,16 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.610760117083036</v>
+        <v>-4.701383936916182</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.263598945068644</v>
+        <v>2.227349417135386</v>
       </c>
       <c r="F2076" t="n">
         <v>1.147041339213749</v>
@@ -49316,16 +49316,16 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409565</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.511096612999373</v>
+        <v>-4.601720432832519</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.306496685433514</v>
+        <v>2.270247157500255</v>
       </c>
       <c r="F2077" t="n">
         <v>1.210228422417435</v>
@@ -49339,16 +49339,16 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.521412711165725</v>
+        <v>-4.612036530998871</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.515275079445031</v>
+        <v>2.479025551511773</v>
       </c>
       <c r="F2078" t="n">
         <v>1.210228422417435</v>
@@ -49362,16 +49362,16 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762283</v>
+        <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.521318743148353</v>
+        <v>-4.611942562981499</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.51449133356407</v>
+        <v>2.478241805630812</v>
       </c>
       <c r="F2079" t="n">
         <v>1.210598283764753</v>
@@ -49385,16 +49385,16 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988014</v>
+        <v>3.633213467988016</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.528537567348197</v>
+        <v>-4.619161387181343</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.505835789828486</v>
+        <v>2.469586261895228</v>
       </c>
       <c r="F2080" t="n">
         <v>1.210598283764753</v>
@@ -49408,16 +49408,16 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740921</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.527589144230158</v>
+        <v>-4.618212964063305</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.506215159075701</v>
+        <v>2.469965631142443</v>
       </c>
       <c r="F2081" t="n">
         <v>1.210598283764753</v>
@@ -49431,16 +49431,16 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.684657602485782</v>
+        <v>-4.775281422318928</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.456115383754544</v>
+        <v>2.419865855821286</v>
       </c>
       <c r="F2082" t="n">
         <v>1.210598283764753</v>
@@ -49454,16 +49454,16 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.67866535569697</v>
+        <v>-4.769289175530116</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.460458280894456</v>
+        <v>2.424208752961198</v>
       </c>
       <c r="F2083" t="n">
         <v>1.210598283764753</v>
@@ -49477,16 +49477,16 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.590107394566203</v>
+        <v>-4.680731214399349</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.489535601364532</v>
+        <v>2.453286073431274</v>
       </c>
       <c r="F2084" t="n">
         <v>1.210598283764753</v>
@@ -49500,16 +49500,16 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.572348317063128</v>
+        <v>-4.662972136896275</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.495947909804758</v>
+        <v>2.459698381871499</v>
       </c>
       <c r="F2085" t="n">
         <v>1.210598283764753</v>
@@ -49523,16 +49523,16 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.472718166014061</v>
+        <v>-4.563341985847207</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.548582156132972</v>
+        <v>2.512332628199713</v>
       </c>
       <c r="F2086" t="n">
         <v>1.310228434813821</v>
@@ -49546,16 +49546,16 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455269</v>
+        <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.522117674703072</v>
+        <v>-4.612741494536218</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.717976618156094</v>
+        <v>2.681727090222835</v>
       </c>
       <c r="F2087" t="n">
         <v>1.320487268245566</v>
@@ -49569,16 +49569,16 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.74907805896313</v>
+        <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.315433201060696</v>
+        <v>-4.406057020893842</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.787839080715906</v>
+        <v>2.751589552782647</v>
       </c>
       <c r="F2088" t="n">
         <v>1.527171741887941</v>
@@ -49592,16 +49592,16 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.74028438916254</v>
+        <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.349590096058222</v>
+        <v>-4.440213915891368</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.776177836371001</v>
+        <v>2.739928308437742</v>
       </c>
       <c r="F2089" t="n">
         <v>1.443587972347129</v>
@@ -49615,16 +49615,16 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.78248211565238</v>
+        <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.257000616996765</v>
+        <v>-4.347624436829912</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.16671074198525</v>
+        <v>3.130461214051992</v>
       </c>
       <c r="F2090" t="n">
         <v>1.443587972347129</v>
@@ -49638,16 +49638,16 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108669</v>
+        <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
         <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.316889244820316</v>
+        <v>-4.407513064653462</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.147318402422933</v>
+        <v>3.111068874489675</v>
       </c>
       <c r="F2091" t="n">
         <v>1.429466057659664</v>
@@ -49661,16 +49661,16 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.83520244110356</v>
+        <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
         <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.264672935023974</v>
+        <v>-4.35529675485712</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.218034867664998</v>
+        <v>3.181785339731739</v>
       </c>
       <c r="F2092" t="n">
         <v>1.429466057659664</v>
@@ -49684,16 +49684,16 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047742</v>
+        <v>3.821827147047744</v>
       </c>
       <c r="C2093" t="n">
         <v>4.933074436198346</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.232775417938728</v>
+        <v>-4.323399237771874</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.239607844709107</v>
+        <v>3.203358316775849</v>
       </c>
       <c r="F2093" t="n">
         <v>1.46136357474491</v>
@@ -49707,16 +49707,16 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650751</v>
+        <v>3.825268416650752</v>
       </c>
       <c r="C2094" t="n">
         <v>4.928712020237543</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.247530742138869</v>
+        <v>-4.338154561972015</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.229343299068248</v>
+        <v>3.193093771134989</v>
       </c>
       <c r="F2094" t="n">
         <v>1.46136357474491</v>
@@ -49730,16 +49730,16 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135744</v>
+        <v>3.845044666135746</v>
       </c>
       <c r="C2095" t="n">
         <v>4.919636523653823</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.198066118768957</v>
+        <v>-4.288689938602103</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.240053651832492</v>
+        <v>3.203804123899234</v>
       </c>
       <c r="F2095" t="n">
         <v>1.510828198114822</v>
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.738349511211419</v>
+        <v>3.724135320951298</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.840707459776846</v>
+        <v>4.916044191368758</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.198066118768957</v>
+        <v>-4.204794195562132</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.240053651832492</v>
+        <v>3.233770088830156</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.510828198114822</v>
+        <v>1.594723941154793</v>
       </c>
       <c r="G2096" t="n">
-        <v>4.833771256763214</v>
+        <v>5.872878556061633</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240923.xlsx
+++ b/tame_output/ON/bt/strategyON_20240923.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-40.2%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-69.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.8%</t>
+          <t>421.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-582.1%</t>
+          <t>-565.1%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-52.8%</t>
+          <t>-46.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>112.9%</t>
+          <t>113.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-64.5%</t>
+          <t>-68.3%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>134.8%</t>
+          <t>133.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>141.3%</t>
+          <t>139.0%</t>
         </is>
       </c>
     </row>
@@ -49069,10 +49069,10 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.6049860698055</v>
+        <v>-4.514362249972354</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.074020086628502</v>
+        <v>2.11026961456176</v>
       </c>
       <c r="F2066" t="n">
         <v>1.221063841660525</v>
@@ -49092,10 +49092,10 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.421774406672405</v>
+        <v>-4.331150586839259</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.149735701345786</v>
+        <v>2.185985229279044</v>
       </c>
       <c r="F2067" t="n">
         <v>1.221063841660525</v>
@@ -49115,10 +49115,10 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.350052959658554</v>
+        <v>-4.259429139825408</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.144215465999216</v>
+        <v>2.180464993932474</v>
       </c>
       <c r="F2068" t="n">
         <v>1.292785288674375</v>
@@ -49138,10 +49138,10 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.327679934050848</v>
+        <v>-4.237056114217702</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.10008042216347</v>
+        <v>2.136329950096728</v>
       </c>
       <c r="F2069" t="n">
         <v>1.304041039787277</v>
@@ -49161,10 +49161,10 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.360696229961593</v>
+        <v>-4.270072410128447</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.272072108684527</v>
+        <v>2.308321636617785</v>
       </c>
       <c r="F2070" t="n">
         <v>1.234603663120525</v>
@@ -49184,10 +49184,10 @@
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.349168594311984</v>
+        <v>-4.258544774478838</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.268604388772619</v>
+        <v>2.304853916705878</v>
       </c>
       <c r="F2071" t="n">
         <v>1.293604321321888</v>
@@ -49207,10 +49207,10 @@
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.446510095654353</v>
+        <v>-4.355886275821207</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.23333590075746</v>
+        <v>2.269585428690719</v>
       </c>
       <c r="F2072" t="n">
         <v>1.249184139156399</v>
@@ -49230,10 +49230,10 @@
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.532366124994319</v>
+        <v>-4.441742305161173</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.200244571214312</v>
+        <v>2.236494099147571</v>
       </c>
       <c r="F2073" t="n">
         <v>1.206808069930264</v>
@@ -49253,16 +49253,16 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.621708092337729</v>
+        <v>-4.450579102577293</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.14692698609745</v>
+        <v>2.215378582001625</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.171899505946087</v>
+        <v>1.199365897288914</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.699106350913942</v>
+        <v>4.715586185719638</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.713090654903188</v>
+        <v>-4.541961665142751</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.120538472116316</v>
+        <v>2.188990068020491</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.135334621226742</v>
+        <v>1.162801012569569</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.687331931127384</v>
+        <v>4.70381176593308</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.701383936916182</v>
+        <v>-4.530254947155745</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.227349417135386</v>
+        <v>2.295801013039561</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.147041339213749</v>
+        <v>1.174507730556575</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.796484219743856</v>
+        <v>4.812964054549552</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409565</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.601720432832519</v>
+        <v>-4.430591443072083</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.270247157500255</v>
+        <v>2.33869875340443</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.210228422417435</v>
+        <v>1.174507730556575</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.837428808397473</v>
+        <v>4.815996393280956</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.612036530998871</v>
+        <v>-4.440907541238435</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.479025551511773</v>
+        <v>2.547477147415948</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.210228422417435</v>
+        <v>1.174507730556575</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.050333641675531</v>
+        <v>5.028901226559015</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.611942562981499</v>
+        <v>-4.440813573221062</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.478241805630812</v>
+        <v>2.546693401534986</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.210598283764753</v>
+        <v>1.174877591903893</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.049734225396011</v>
+        <v>5.028301810279495</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988016</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.619161387181343</v>
+        <v>-4.448032397420906</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.469586261895228</v>
+        <v>2.538037857799402</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.210598283764753</v>
+        <v>1.174877591903893</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.043966211340365</v>
+        <v>5.022533796223849</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.618212964063305</v>
+        <v>-4.447083974302868</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.469965631142443</v>
+        <v>2.538417227046618</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.210598283764753</v>
+        <v>1.174877591903893</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.043966211340365</v>
+        <v>5.022533796223849</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.775281422318928</v>
+        <v>-4.604152432558491</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.419865855821286</v>
+        <v>2.48831745172546</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.210598283764753</v>
+        <v>1.174877591903893</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.056693819321457</v>
+        <v>5.035261404204941</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.769289175530116</v>
+        <v>-4.59816018576968</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.424208752961198</v>
+        <v>2.492660348865373</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.210598283764753</v>
+        <v>1.174877591903893</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.058639817745845</v>
+        <v>5.037207402629329</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.680731214399349</v>
+        <v>-4.509602224638912</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.453286073431274</v>
+        <v>2.521737669335448</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.210598283764753</v>
+        <v>1.174877591903893</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.052293953763614</v>
+        <v>5.030861538647097</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.662972136896275</v>
+        <v>-4.491843147135838</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.459698381871499</v>
+        <v>2.528149977775674</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.210598283764753</v>
+        <v>1.174877591903893</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.051602631202609</v>
+        <v>5.030170216086093</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.563341985847207</v>
+        <v>-4.39221299608677</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.512332628199713</v>
+        <v>2.580784224103888</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.310228434813821</v>
+        <v>1.274507742952961</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.124162907740637</v>
+        <v>5.10273049262412</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.612741494536218</v>
+        <v>-4.441612504775781</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.681727090222835</v>
+        <v>2.750178686127009</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.320487268245566</v>
+        <v>1.284766576384706</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.31947247329841</v>
+        <v>5.298040058181893</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.406057020893842</v>
+        <v>-4.234928031133405</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.751589552782647</v>
+        <v>2.820041148686822</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.527171741887941</v>
+        <v>1.491451050027081</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.430671830586697</v>
+        <v>5.409239415470181</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.440213915891368</v>
+        <v>-4.269084926130931</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.739928308437742</v>
+        <v>2.808379904341916</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.443587972347129</v>
+        <v>1.407867280486269</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.382523082516315</v>
+        <v>5.361090667399798</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.347624436829912</v>
+        <v>-4.176495447069475</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.130461214051992</v>
+        <v>3.198912809956167</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.443587972347129</v>
+        <v>1.407867280486269</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.736020196505982</v>
+        <v>5.714587781389466</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.407513064653462</v>
+        <v>-4.236384074893025</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.111068874489675</v>
+        <v>3.17952047039385</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.429466057659664</v>
+        <v>1.393745365798804</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.732110159260607</v>
+        <v>5.710677744144091</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.35529675485712</v>
+        <v>-4.184167765096683</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.181785339731739</v>
+        <v>3.250236935635914</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.429466057659664</v>
+        <v>1.393745365798804</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.781940100584134</v>
+        <v>5.760507685467618</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.933074436198346</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.323399237771874</v>
+        <v>-4.152270248011438</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.203358316775849</v>
+        <v>3.271809912680023</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.46136357474491</v>
+        <v>1.42564288288405</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.809892581045292</v>
+        <v>5.788460165928776</v>
       </c>
     </row>
     <row r="2094">
@@ -49713,16 +49713,16 @@
         <v>4.928712020237543</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.338154561972015</v>
+        <v>-4.167025572211578</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.193093771134989</v>
+        <v>3.261545367039164</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.46136357474491</v>
+        <v>1.42564288288405</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.805530165084489</v>
+        <v>5.784097749967973</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135746</v>
+        <v>3.845044666135747</v>
       </c>
       <c r="C2095" t="n">
         <v>4.919636523653823</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.288689938602103</v>
+        <v>-4.117560948841667</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.203804123899234</v>
+        <v>3.272255719803408</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.510828198114822</v>
+        <v>1.475107506253962</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.826133442522717</v>
+        <v>5.804701027406201</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.724135320951298</v>
+        <v>3.722146322598437</v>
       </c>
       <c r="C2096" t="n">
         <v>4.916044191368758</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.204794195562132</v>
+        <v>-4.035759848413893</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.233770088830156</v>
+        <v>3.301383827689452</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.594723941154793</v>
+        <v>1.556908606681735</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.872878556061633</v>
+        <v>5.850189355377799</v>
       </c>
     </row>
   </sheetData>
